--- a/uploads/UPLOAD-TEMPLATE/STAFFS-TRANSFER-TEMPLATE.xlsx
+++ b/uploads/UPLOAD-TEMPLATE/STAFFS-TRANSFER-TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSH TEMPLATE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC29C6FD-E5A0-4C9E-A15E-B2CD496F3BEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E238E9E-BEAD-4446-869E-4717A0072512}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{8DE630E0-0B89-4DDE-A92E-DF514EA9A919}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
-    <t>Location</t>
-  </si>
-  <si>
     <t>Staff Code</t>
   </si>
   <si>
@@ -39,9 +36,6 @@
     <t>Salary Rate</t>
   </si>
   <si>
-    <t>Agency</t>
-  </si>
-  <si>
     <t>Effectivity Date</t>
   </si>
   <si>
@@ -64,6 +58,12 @@
   </si>
   <si>
     <t>* delete this line and above sample data on actual uploading</t>
+  </si>
+  <si>
+    <t>New Agency</t>
+  </si>
+  <si>
+    <t>New Location</t>
   </si>
 </sst>
 </file>
@@ -466,36 +466,36 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D2">
         <v>123</v>
@@ -507,17 +507,17 @@
         <v>46230</v>
       </c>
       <c r="G2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
